--- a/data/trans_orig/P78C_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P78C_2023-Clase-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W60"/>
+  <dimension ref="A1:W52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba la persona sustentadora principal en 2023</t>
+          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba la persona sustentadora principal en 2023 (tasa de respuesta: 98,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>243839</t>
+          <t>242750</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>292011</t>
+          <t>288295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>292001</t>
+          <t>292391</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>325350</t>
+          <t>324671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>547716</t>
+          <t>546332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>605492</t>
+          <t>604182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,58%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65904</t>
+          <t>65682</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97094</t>
+          <t>98539</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>34738</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55240</t>
+          <t>55462</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107720</t>
+          <t>106101</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146513</t>
+          <t>143573</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19689</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>750</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23261</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17181</t>
+          <t>17306</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39237</t>
+          <t>38952</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17173</t>
+          <t>17134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>25826</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49775</t>
+          <t>49656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24118</t>
+          <t>23552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46138</t>
+          <t>45415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>11288</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24202</t>
+          <t>23871</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38506</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62734</t>
+          <t>62624</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29122</t>
+          <t>30215</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8786</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>16123</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35110</t>
+          <t>33593</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50986</t>
+          <t>51883</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80680</t>
+          <t>79671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48566</t>
+          <t>48545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73351</t>
+          <t>73983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106584</t>
+          <t>107792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144987</t>
+          <t>145588</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>324689</t>
+          <t>323397</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>358906</t>
+          <t>359074</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>314001</t>
+          <t>314470</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>337223</t>
+          <t>337096</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>648921</t>
+          <t>647476</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>689120</t>
+          <t>687551</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,7%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52157</t>
+          <t>52558</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81900</t>
+          <t>80515</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18128</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33648</t>
+          <t>32946</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71928</t>
+          <t>73924</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106366</t>
+          <t>106239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>13924</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21215</t>
+          <t>21000</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24095</t>
+          <t>24039</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46774</t>
+          <t>47129</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11190</t>
+          <t>11907</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24224</t>
+          <t>24214</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39653</t>
+          <t>38885</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65008</t>
+          <t>64477</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74147</t>
+          <t>87089</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>365282</t>
+          <t>365605</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48070</t>
+          <t>48587</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68855</t>
+          <t>69532</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>114009</t>
+          <t>122502</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>412066</t>
+          <t>412076</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15921</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70245</t>
+          <t>69861</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19808</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71060</t>
+          <t>71989</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>522645</t>
+          <t>498270</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>580212</t>
+          <t>572906</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>13981</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>71332</t>
+          <t>70381</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>11290</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22861</t>
+          <t>23123</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>21650</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>86433</t>
+          <t>87727</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2391</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17278</t>
+          <t>17936</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>36943</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>166067</t>
+          <t>170071</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70421</t>
+          <t>70676</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>90577</t>
+          <t>90631</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>76805</t>
+          <t>80648</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>267041</t>
+          <t>268589</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>773746</t>
+          <t>770932</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>828376</t>
+          <t>828692</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>799132</t>
+          <t>798515</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>903362</t>
+          <t>903981</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1587573</t>
+          <t>1588643</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1757069</t>
+          <t>1755104</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,62%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28115</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>58225</t>
+          <t>59116</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25075</t>
+          <t>24840</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>74838</t>
+          <t>76933</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -3680,97 +3680,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>4269</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>1269</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>4812</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>3838</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>4227</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -3793,12 +3793,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>20949</t>
+          <t>19819</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>45260</t>
+          <t>42898</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>24995</t>
+          <t>25240</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>30082</t>
+          <t>30586</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>62024</t>
+          <t>61091</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12570</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4069,47 +4069,47 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>9690</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>4978</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>17121</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
           <t>0,85%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>9690</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>5383</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>17588</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>132763</t>
+          <t>131411</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>178335</t>
+          <t>177528</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>49842</t>
+          <t>49617</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>123920</t>
+          <t>126821</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>165268</t>
+          <t>163687</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>287563</t>
+          <t>284902</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>411084</t>
+          <t>413025</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>445061</t>
+          <t>446035</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>501325</t>
+          <t>526895</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>772651</t>
+          <t>773465</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>913117</t>
+          <t>948587</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1209193</t>
+          <t>1208441</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21005</t>
+          <t>20312</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>26898</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -4588,97 +4588,97 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>1667</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>1255</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>1381</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4701,97 +4701,97 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>1667</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5191</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>4475</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>4861</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>4669</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>282699</t>
+          <t>263068</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>311425</t>
+          <t>283557</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12744</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5040,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>40844</t>
+          <t>39548</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>21770</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>42993</t>
+          <t>44507</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>37008</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>73568</t>
+          <t>73187</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -5260,107 +5260,107 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2069056</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1511621</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2259046</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2239843</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2056392</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2345928</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4308899</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3675501</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4553587</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,13%</t>
         </is>
       </c>
     </row>
@@ -5373,107 +5373,107 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>273</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>239383</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>180573</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>274135</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94989</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72864</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>114475</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>422</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334373</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>282440</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>376526</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -5486,107 +5486,107 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24226</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12364</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13591</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31003</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -5599,107 +5599,107 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273600</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1034839</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15872</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>289472</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42475</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1087781</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -5712,107 +5712,107 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>143</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115637</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>87131</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138086</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>103</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129892</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55128</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>386020</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>246</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>245529</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>169096</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>561776</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -5825,107 +5825,107 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37166</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25592</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>52644</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14241</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21738</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>68</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51407</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38379</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>65968</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -5938,107 +5938,107 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>435</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370674</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285014</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>416454</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>484</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>283042</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>222599</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>321908</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>919</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>653716</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>556158</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>720349</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -6051,1032 +6051,123 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3120283</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3120283</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3120283</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2783396</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2783396</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2783396</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5903679</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5903679</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5903679</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Otro asalariado</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>2226</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>2069056</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>1561626</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>2257952</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>66,31%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>50,05%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>72,36%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>3232</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>2239843</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>2064466</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>2337776</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>80,47%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>74,17%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>83,99%</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>5458</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>4308899</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>3631654</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>4546096</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>72,99%</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>61,52%</t>
-        </is>
-      </c>
-      <c r="W52" s="2" t="inlineStr">
-        <is>
-          <t>77,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n"/>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Capataz, supervisor o encargado</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>239383</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>182493</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>276393</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>8,86%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>94989</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>71929</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>114589</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>334373</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>285979</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>377571</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="W53" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n"/>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>Gerente de una empresa con menos de 10 asalariados</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>14767</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>8037</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>22914</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>5517</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>2446</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>11702</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>20284</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>13143</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
-          <t>30172</t>
-        </is>
-      </c>
-      <c r="U54" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="W54" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n"/>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>Gerente de una empresa con 10 o más asalariados</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>273600</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>27612</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>960925</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>30,8%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>15872</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>9867</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>24598</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>289472</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>42912</t>
-        </is>
-      </c>
-      <c r="T55" s="2" t="inlineStr">
-        <is>
-          <t>1262777</t>
-        </is>
-      </c>
-      <c r="U55" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="W55" s="2" t="inlineStr">
-        <is>
-          <t>21,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n"/>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>Trabajador por cuenta propia, con menos de 10 asalariados</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>115637</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>84408</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>139519</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>129892</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>57364</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>378993</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>13,62%</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>245529</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>168657</t>
-        </is>
-      </c>
-      <c r="T56" s="2" t="inlineStr">
-        <is>
-          <t>477927</t>
-        </is>
-      </c>
-      <c r="U56" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="V56" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="W56" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="n"/>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Trabajador por cuenta propia, con 10 o más asalariados</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>37166</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>24127</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>50340</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>14241</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>8840</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>21507</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="inlineStr">
-        <is>
-          <t>51407</t>
-        </is>
-      </c>
-      <c r="S57" s="2" t="inlineStr">
-        <is>
-          <t>39383</t>
-        </is>
-      </c>
-      <c r="T57" s="2" t="inlineStr">
-        <is>
-          <t>67998</t>
-        </is>
-      </c>
-      <c r="U57" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="W57" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="n"/>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Trabajador por cuenta propia, sin asalariados</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>370674</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>276797</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>418957</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>11,88%</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>8,87%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>13,43%</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>283042</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>218964</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>322290</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>10,17%</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>11,58%</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
-          <t>919</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>653716</t>
-        </is>
-      </c>
-      <c r="S58" s="2" t="inlineStr">
-        <is>
-          <t>554164</t>
-        </is>
-      </c>
-      <c r="T58" s="2" t="inlineStr">
-        <is>
-          <t>724499</t>
-        </is>
-      </c>
-      <c r="U58" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="V58" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="W58" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="n"/>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>3171</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>3120283</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>3120283</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>3120283</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>4028</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>2783396</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>2783396</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>2783396</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>7199</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>5903679</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="inlineStr">
-        <is>
-          <t>5903679</t>
-        </is>
-      </c>
-      <c r="T59" s="2" t="inlineStr">
-        <is>
-          <t>5903679</t>
-        </is>
-      </c>
-      <c r="U59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A44:A51"/>
     <mergeCell ref="A4:A11"/>
     <mergeCell ref="A12:A19"/>
-    <mergeCell ref="A52:A59"/>
     <mergeCell ref="A20:A27"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>

--- a/data/trans_orig/P78C_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P78C_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>267187</t>
+          <t>285170</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>242750</t>
+          <t>260274</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>288295</t>
+          <t>309506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>309179</t>
+          <t>331611</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>292391</t>
+          <t>314594</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>324671</t>
+          <t>350643</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>576365</t>
+          <t>616781</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>546332</t>
+          <t>585980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>604182</t>
+          <t>646284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80940</t>
+          <t>90064</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65682</t>
+          <t>72838</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98539</t>
+          <t>108150</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43827</t>
+          <t>48480</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34738</t>
+          <t>37980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55462</t>
+          <t>60944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>124767</t>
+          <t>138543</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106101</t>
+          <t>118906</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143573</t>
+          <t>160015</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20971</t>
+          <t>21901</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>16292</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>9671</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>25013</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25515</t>
+          <t>28774</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17306</t>
+          <t>19205</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38952</t>
+          <t>44492</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17134</t>
+          <t>21030</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>36142</t>
+          <t>41760</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25826</t>
+          <t>30071</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49656</t>
+          <t>57296</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33090</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23552</t>
+          <t>25355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45415</t>
+          <t>45591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16523</t>
+          <t>17787</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11288</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23871</t>
+          <t>25629</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>49613</t>
+          <t>52115</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>41453</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62624</t>
+          <t>65004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19544</t>
+          <t>22361</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>32372</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>9065</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>23920</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>33593</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>64623</t>
+          <t>74872</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51883</t>
+          <t>61090</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79671</t>
+          <t>91967</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,32 +1438,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60333</t>
+          <t>69124</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48545</t>
+          <t>55938</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73983</t>
+          <t>84577</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>124956</t>
+          <t>143996</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107792</t>
+          <t>124341</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145588</t>
+          <t>165955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -1516,17 +1516,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>503345</t>
+          <t>548677</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503345</t>
+          <t>548677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>503345</t>
+          <t>548677</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1551,17 +1551,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>446875</t>
+          <t>487744</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>446875</t>
+          <t>487744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>446875</t>
+          <t>487744</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>950220</t>
+          <t>1036421</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>950220</t>
+          <t>1036421</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>950220</t>
+          <t>1036421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>341830</t>
+          <t>361062</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>323397</t>
+          <t>340831</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>359074</t>
+          <t>379301</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>326393</t>
+          <t>358277</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>314470</t>
+          <t>346034</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>337096</t>
+          <t>369969</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>668223</t>
+          <t>719339</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>647476</t>
+          <t>695412</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>687551</t>
+          <t>740265</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>65231</t>
+          <t>71730</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52558</t>
+          <t>57350</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80515</t>
+          <t>89928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24669</t>
+          <t>27822</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>20475</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32946</t>
+          <t>37696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>89900</t>
+          <t>99552</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73924</t>
+          <t>82389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106239</t>
+          <t>118996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>742</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,17 +1929,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13924</t>
+          <t>14654</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>7978</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>14636</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>13939</t>
+          <t>15921</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21000</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>987</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>509</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33511</t>
+          <t>37227</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>26748</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47129</t>
+          <t>51174</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>14004</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>29758</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>50754</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38885</t>
+          <t>45734</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64477</t>
+          <t>73482</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -2424,17 +2424,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>450606</t>
+          <t>481488</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>450606</t>
+          <t>481488</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>450606</t>
+          <t>481488</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>380789</t>
+          <t>420969</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>380789</t>
+          <t>420969</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>380789</t>
+          <t>420969</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>831395</t>
+          <t>902457</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>831395</t>
+          <t>902457</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>831395</t>
+          <t>902457</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>224375</t>
+          <t>248089</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87089</t>
+          <t>226336</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>365605</t>
+          <t>272940</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>57979</t>
+          <t>62143</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48587</t>
+          <t>51108</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69532</t>
+          <t>74501</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>282354</t>
+          <t>310232</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122502</t>
+          <t>286179</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>412076</t>
+          <t>336899</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>51,59%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40593</t>
+          <t>43379</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>32765</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69861</t>
+          <t>56764</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>46609</t>
+          <t>50791</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20774</t>
+          <t>39076</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71989</t>
+          <t>64803</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6896</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>661</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2446</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>246529</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>834</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>498270</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>246529</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>826</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>572906</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>41061</t>
+          <t>44092</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13981</t>
+          <t>34108</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>70381</t>
+          <t>57720</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,32 +3028,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16735</t>
+          <t>19144</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11290</t>
+          <t>13607</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>26898</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>57796</t>
+          <t>63236</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21650</t>
+          <t>49598</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>87727</t>
+          <t>77956</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -3106,32 +3106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>12417</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17936</t>
+          <t>23107</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3141,32 +3141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3176,32 +3176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21301</t>
+          <t>27210</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -3219,32 +3219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>101223</t>
+          <t>114426</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36943</t>
+          <t>93732</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>170071</t>
+          <t>134182</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3254,32 +3254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>80528</t>
+          <t>91973</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70676</t>
+          <t>80220</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>90631</t>
+          <t>103460</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3289,32 +3289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>181751</t>
+          <t>206399</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>80648</t>
+          <t>183482</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>268589</t>
+          <t>231798</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -3332,17 +3332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>663965</t>
+          <t>467286</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>663965</t>
+          <t>467286</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>663965</t>
+          <t>467286</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3367,17 +3367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>165335</t>
+          <t>185780</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>165335</t>
+          <t>185780</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>165335</t>
+          <t>185780</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3402,17 +3402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>829300</t>
+          <t>653065</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>829300</t>
+          <t>653065</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>829300</t>
+          <t>653065</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>801951</t>
+          <t>874120</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>770932</t>
+          <t>844245</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>828692</t>
+          <t>901981</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>842542</t>
+          <t>709333</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>798515</t>
+          <t>690105</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>903981</t>
+          <t>728507</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1644493</t>
+          <t>1583453</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1588643</t>
+          <t>1547567</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1755104</t>
+          <t>1619150</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>40443</t>
+          <t>45122</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28824</t>
+          <t>31919</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59116</t>
+          <t>63869</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15239</t>
+          <t>18102</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24840</t>
+          <t>26686</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>55683</t>
+          <t>63224</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>47076</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>76933</t>
+          <t>85248</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -3823,32 +3823,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,32 +3858,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>700</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -3901,32 +3901,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>29371</t>
+          <t>32199</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>42898</t>
+          <t>45146</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3936,32 +3936,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>15587</t>
+          <t>17316</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>11307</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25240</t>
+          <t>25457</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3971,32 +3971,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>44958</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>30586</t>
+          <t>37778</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>61091</t>
+          <t>66173</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -4014,67 +4014,67 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>4507</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>9354</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>3720</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>1373</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>8918</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4084,32 +4084,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>17121</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -4127,32 +4127,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>152452</t>
+          <t>167350</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>131411</t>
+          <t>144332</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>177528</t>
+          <t>196890</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4162,32 +4162,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>92883</t>
+          <t>101925</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>85870</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>126821</t>
+          <t>117952</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>245335</t>
+          <t>269275</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>163687</t>
+          <t>242163</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>284902</t>
+          <t>301586</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -4240,17 +4240,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1030187</t>
+          <t>1125528</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1030187</t>
+          <t>1125528</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1030187</t>
+          <t>1125528</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>972813</t>
+          <t>854794</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>972813</t>
+          <t>854794</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>972813</t>
+          <t>854794</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>2003000</t>
+          <t>1980323</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2003000</t>
+          <t>1980323</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2003000</t>
+          <t>1980323</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>433713</t>
+          <t>525074</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>413025</t>
+          <t>509888</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>446035</t>
+          <t>536176</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>703751</t>
+          <t>756473</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>526895</t>
+          <t>744995</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>773465</t>
+          <t>765900</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1137464</t>
+          <t>1281547</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>948587</t>
+          <t>1261936</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1208441</t>
+          <t>1297499</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>12176</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>21738</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>19019</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>28081</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -4809,22 +4809,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>13082</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4844,32 +4844,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>73914</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>263068</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4879,32 +4879,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>79223</t>
+          <t>11447</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>6165</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>283557</t>
+          <t>21006</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4932,12 +4932,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4992,22 +4992,22 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -5035,32 +5035,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>18866</t>
+          <t>17851</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>39548</t>
+          <t>28870</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5070,32 +5070,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>32056</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>22623</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>44507</t>
+          <t>43097</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5105,32 +5105,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>50921</t>
+          <t>51428</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>37347</t>
+          <t>40344</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>73187</t>
+          <t>65562</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -5148,17 +5148,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>472180</t>
+          <t>563996</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>472180</t>
+          <t>563996</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>472180</t>
+          <t>563996</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,17 +5183,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>817584</t>
+          <t>804623</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>817584</t>
+          <t>804623</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>817584</t>
+          <t>804623</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,17 +5218,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1289764</t>
+          <t>1368619</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1289764</t>
+          <t>1368619</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1289764</t>
+          <t>1368619</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2069056</t>
+          <t>2293516</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1511621</t>
+          <t>2239887</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2259046</t>
+          <t>2345962</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2239843</t>
+          <t>2217837</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2056392</t>
+          <t>2183255</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2345928</t>
+          <t>2252303</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>4308899</t>
+          <t>4511353</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3675501</t>
+          <t>4452834</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4553587</t>
+          <t>4581800</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,12%</t>
         </is>
       </c>
     </row>
@@ -5378,32 +5378,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>239383</t>
+          <t>263101</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>180573</t>
+          <t>231360</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>274135</t>
+          <t>298125</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5413,32 +5413,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>94989</t>
+          <t>108029</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>72864</t>
+          <t>92122</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>114475</t>
+          <t>125536</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5448,32 +5448,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>334373</t>
+          <t>371130</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>282440</t>
+          <t>333676</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>376526</t>
+          <t>409097</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -5491,32 +5491,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>15637</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>24226</t>
+          <t>25241</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5526,32 +5526,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>12364</t>
+          <t>12617</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5561,32 +5561,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>22627</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>13591</t>
+          <t>15082</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -5604,32 +5604,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>273600</t>
+          <t>33668</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>28596</t>
+          <t>22974</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1034839</t>
+          <t>50130</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5639,32 +5639,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>15872</t>
+          <t>19059</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>24081</t>
+          <t>27915</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5674,32 +5674,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>289472</t>
+          <t>52727</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>39718</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1087781</t>
+          <t>69812</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -5717,102 +5717,102 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>115637</t>
+          <t>124363</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>87131</t>
+          <t>104218</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>138086</t>
+          <t>146540</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>67873</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>55481</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>83725</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>192235</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>169140</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>220598</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
           <t>3,71%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>129892</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>55128</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>386020</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>13,87%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>245529</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>169096</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>561776</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -5830,102 +5830,102 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>37166</t>
+          <t>44965</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>25592</t>
+          <t>33532</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>52644</t>
+          <t>60758</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>10490</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>25505</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>61715</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>48480</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>78758</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>14241</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>9219</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>21738</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>51407</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>38379</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t>65968</t>
-        </is>
-      </c>
-      <c r="U49" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -5943,32 +5943,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>370674</t>
+          <t>411726</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>285014</t>
+          <t>375194</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>416454</t>
+          <t>447714</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>283042</t>
+          <t>317373</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>222599</t>
+          <t>289197</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>321908</t>
+          <t>344708</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>653716</t>
+          <t>729099</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>556158</t>
+          <t>683443</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>720349</t>
+          <t>779876</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -6056,17 +6056,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3120283</t>
+          <t>3186976</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3120283</t>
+          <t>3186976</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3120283</t>
+          <t>3186976</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>2783396</t>
+          <t>2753910</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>2783396</t>
+          <t>2753910</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2783396</t>
+          <t>2753910</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6126,17 +6126,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>5903679</t>
+          <t>5940886</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>5903679</t>
+          <t>5940886</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>5903679</t>
+          <t>5940886</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
